--- a/spec/AGCP_Requirements_Traceability_Matrix_(RTM).xlsx
+++ b/spec/AGCP_Requirements_Traceability_Matrix_(RTM).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\business\Sustainable Future Tech Inc\arXiv\PBSAI\AGCP Spec and Package\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{883B1263-E0A6-4DB2-A9BB-A6632D8FD4BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE02A17E-51BC-45CE-B628-1BAD74EC57FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13558" uniqueCount="3092">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13558" uniqueCount="3097">
   <si>
     <t>RTM_ID</t>
   </si>
@@ -9297,6 +9297,21 @@
   </si>
   <si>
     <t>Direct test-generating relationship. Successful Commit Boundary processing necessarily establishes the authoritative commitment event, permits applicable lifecycle progression, and finalizes Governance Evidence. Post-commit execution-outcome evidence and separately defined operational controls are verified only where applicable, but their conditional applicability does not make the underlying NS-to-CR relationship conditional. Approved by the AGCP Specification Owner following Priority 3 synchronization and validation on 2026-07-19.</t>
+  </si>
+  <si>
+    <t>Submit -&gt; Authorized</t>
+  </si>
+  <si>
+    <t>Submit -&gt; Pending HITL</t>
+  </si>
+  <si>
+    <t>Submit -&gt; Rejected (Hard Invariant Failure)</t>
+  </si>
+  <si>
+    <t>HITL Expiration -&gt; Rejected</t>
+  </si>
+  <si>
+    <t>Governance Cancellation -&gt; Rejected</t>
   </si>
 </sst>
 </file>
@@ -9782,7 +9797,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -9800,6 +9815,7 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -10198,8 +10214,8 @@
       <c r="E2" t="s">
         <v>48</v>
       </c>
-      <c r="F2" t="s">
-        <v>49</v>
+      <c r="F2" s="7" t="s">
+        <v>3092</v>
       </c>
       <c r="G2" t="s">
         <v>50</v>
@@ -10306,8 +10322,8 @@
       <c r="E3" t="s">
         <v>48</v>
       </c>
-      <c r="F3" t="s">
-        <v>78</v>
+      <c r="F3" s="7" t="s">
+        <v>3093</v>
       </c>
       <c r="G3" t="s">
         <v>79</v>
@@ -10412,8 +10428,8 @@
       <c r="E4" t="s">
         <v>48</v>
       </c>
-      <c r="F4" t="s">
-        <v>93</v>
+      <c r="F4" s="7" t="s">
+        <v>3094</v>
       </c>
       <c r="G4" t="s">
         <v>94</v>
@@ -11902,8 +11918,8 @@
       <c r="E18" t="s">
         <v>48</v>
       </c>
-      <c r="F18" t="s">
-        <v>278</v>
+      <c r="F18" s="7" t="s">
+        <v>3095</v>
       </c>
       <c r="G18" t="s">
         <v>279</v>
@@ -12008,8 +12024,8 @@
       <c r="E19" t="s">
         <v>48</v>
       </c>
-      <c r="F19" t="s">
-        <v>289</v>
+      <c r="F19" s="7" t="s">
+        <v>3096</v>
       </c>
       <c r="G19" t="s">
         <v>290</v>
